--- a/docs/Pathway-enrichment/Pathway-enrichment-for-genes-with-DARs-upin-Healthy.vs.Patients.xlsx
+++ b/docs/Pathway-enrichment/Pathway-enrichment-for-genes-with-DARs-upin-Healthy.vs.Patients.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="309">
   <si>
     <t xml:space="preserve">Term</t>
   </si>
@@ -32,163 +32,913 @@
     <t xml:space="preserve">P.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">methylglyoxal reductase (NADPH) (acetol producing) activity</t>
+    <t xml:space="preserve">protein binding</t>
   </si>
   <si>
     <t xml:space="preserve">MF</t>
   </si>
   <si>
-    <t xml:space="preserve">exoribonuclease II activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transmembrane transporter binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">histamine receptor activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">riboflavin transmembrane transporter activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">single-stranded DNA 3'-5' DNA exonuclease activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U2 snRNA binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U1 snRNA binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">single-stranded DNA exodeoxyribonuclease activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U3 snoRNA binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G protein-coupled serotonin receptor activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">central nervous system formation</t>
+    <t xml:space="preserve">binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enzyme regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molecular_function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTPase regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nucleoside-triphosphatase regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immune receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytokine receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enzyme activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molecular function regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signaling receptor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small molecule binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chemokine receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G protein-coupled chemoattractant receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ion binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enzyme binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTPase activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anion binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphotransferase activity, alcohol group as acceptor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guanyl-nucleotide exchange factor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytokine binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">catalytic activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phospholipid binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein kinase binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-C chemokine receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nucleoside phosphate binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nucleotide binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transcription coregulator binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heterocyclic compound binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chemokine binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-C chemokine binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">histone H3 kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transcription corepressor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kinase binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMAD binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">histone kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">histone H2AX kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphoric ester hydrolase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNA-binding transcription factor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transferase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoskeleton-nuclear membrane anchor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lipid binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transcription factor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molecular function activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transferase activity, transferring phosphorus-containing groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">catalytic activity, acting on a protein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purine nucleotide binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non-membrane spanning protein tyrosine kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNA polymerase II-specific DNA-binding transcription factor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carbohydrate derivative binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAD+ nucleosidase activity, cyclic ADP-ribose generating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ribonucleotide binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identical protein binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylserine binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purine ribonucleotide binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adenyl nucleotide binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein-macromolecule adaptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">histone H2AXY142 kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">histone H3Y41 kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molecular adaptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">histone modifying activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein tyrosine kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adenyl ribonucleotide binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modified amino acid binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein serine kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylinositol phosphate phosphatase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cation binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purine ribonucleoside triphosphate binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphotyrosine residue binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein serine/threonine kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylinositol 3-kinase binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-X-C chemokine receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphoric diester hydrolase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein phosphorylated amino acid binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metal ion binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insulin receptor substrate binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein dimerization activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-methylcytosine dioxygenase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5'-deoxynucleotidase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylinositol phosphate 4-phosphatase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nuclear retinoic acid receptor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tumor necrosis factor receptor superfamily binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein tyrosine kinase binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylinositol kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">death receptor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAD+ nucleosidase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylinositol 3-kinase regulatory subunit binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nuclear receptor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signaling adaptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interleukin-1 receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kinase regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein-containing complex binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kinase activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein kinase inhibitor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell adhesion molecule binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molecular transducer activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of response to stimulus</t>
   </si>
   <si>
     <t xml:space="preserve">BP</t>
   </si>
   <si>
-    <t xml:space="preserve">telencephalon cell migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forebrain cell migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of anion channel activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of anion transmembrane transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of axon extension involved in regeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of sprouting of injured axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of axon extension involved in regeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">axon extension involved in regeneration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">central nervous system morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of sprouting of injured axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of protein localization to membrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of monoatomic anion transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of anion channel activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sprouting of injured axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adenylate cyclase-activating serotonin receptor signaling pathway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of monoatomic anion transmembrane transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">riboflavin metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flavin-containing compound metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">riboflavin transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADPH oxidation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">neuroblast migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of transmission of nerve impulse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of protein localization to membrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">serotonin receptor signaling pathway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cuticular plate</t>
+    <t xml:space="preserve">cell activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of multicellular organismal process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lymphocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leukocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of biological process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cellular process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immune system process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hemopoiesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of immune system process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of multicellular organismal process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leukocyte differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular response to stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of developmental process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of signaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular developmental process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T cell activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anatomical structure development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">developmental process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mononuclear cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multicellular organismal process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell surface receptor signaling pathway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular signaling cassette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of response to stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of biological process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of immune system process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locomotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of intracellular signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cellular process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multicellular organism development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell motility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of leukocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lymphocyte differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leukocyte cell-cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of lymphocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell population proliferation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of multicellular organismal process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of multicellular organismal development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell-cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">myeloid cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biological regulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell motility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of locomotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to external stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of developmental process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of leukocyte cell-cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular response to chemical stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of T cell activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cell migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of biological process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inflammatory response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">system development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to peptide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of immune response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to cytokine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of response to external stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of locomotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cell motility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell-cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immune response-regulating cell surface receptor signaling pathway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular response to cytokine stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of hemopoiesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of cellular process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of response to stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defense response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immune response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of small GTPase mediated signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immune response-activating cell surface receptor signaling pathway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lymphocyte proliferation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell population proliferation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leukocyte proliferation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of immune response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anatomical structure morphogenesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of signaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leukocyte migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small GTPase-mediated signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mononuclear cell proliferation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of metabolic process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of biosynthetic process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of macromolecule metabolic process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cell communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of leukocyte differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoplasm</t>
   </si>
   <si>
     <t xml:space="preserve">CC</t>
   </si>
   <si>
-    <t xml:space="preserve">pinceau fiber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">main axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cortical actin cytoskeleton</t>
+    <t xml:space="preserve">cell periphery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plasma membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular anatomical structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external side of plasma membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">side of membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytosol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endomembrane system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoplasmic vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immunological synapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bounding membrane of organelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruffle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell leading edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">membrane raft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular organelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leading edge membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell projection membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">membrane microdomain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golgi membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">organelle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular membrane-bounded organelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruffle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell junction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golgi apparatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">focal adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">late endosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell-substrate junction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">membrane-bounded organelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoplasmic vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">organelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endosome membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nucleoplasm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meiotic nuclear membrane microtubule tethering complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">microtubule organizing center attachment site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nuclear membrane microtubule tethering complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nuclear membrane protein complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lytic vacuole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actin cytoskeleton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vacuole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plasma membrane region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endocytic vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anchoring junction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transcription regulator complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vacuolar membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylinositol 3-kinase complex, class I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylinositol 3-kinase complex, class IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular anatomical structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">podosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">late endosome membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysosomal membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lytic vacuole membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integrin complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromatin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nuclear membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoskeleton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphatidylinositol 3-kinase complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">activin receptor complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">synapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell cortex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phagocytic cup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNA polymerase II transcription regulator complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secretory vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nuclear inner membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secretory granule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell projection</t>
   </si>
   <si>
     <t xml:space="preserve">cortical cytoskeleton</t>
   </si>
   <si>
-    <t xml:space="preserve">tenascin complex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spectrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spectrin-associated cytoskeleton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perineuronal net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9+2 non-motile cilium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kinocilium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perisynaptic extracellular matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juxtaparanode region of axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">synapse-associated extracellular matrix</t>
+    <t xml:space="preserve">lumenal side of endoplasmic reticulum membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golgi apparatus subcompartment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plasma membrane bounded cell projection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transcription repressor complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">early endosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta-catenin-TCF complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trans-Golgi network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MHC protein complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plasma membrane raft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brahma complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npBAF complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lumenal side of membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contractile actin filament bundle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stress fiber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNA polymerase II transcription repressor complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trans-Golgi network membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta-catenin-ICAT complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytolytic granule lumen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derlin-1-VIMP complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integrin alpha1-beta1 complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integrin alpha4-beta7 complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integrin alpha6-beta1 complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interleukin-18 receptor complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extrinsic component of membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bBAF complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endolysosome</t>
   </si>
   <si>
     <t xml:space="preserve">Pathway</t>
@@ -545,13 +1295,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>14778</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1439</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00134444082543206</v>
+        <v>0.00000000000000000000024680720063396</v>
       </c>
     </row>
     <row r="3">
@@ -562,13 +1312,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>17098</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1593</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00201603165204578</v>
+        <v>0.00000000000000000444628812930495</v>
       </c>
     </row>
     <row r="4">
@@ -579,13 +1329,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>136</v>
+        <v>1351</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00366120606792533</v>
+        <v>0.00000000000293994584841991</v>
       </c>
     </row>
     <row r="5">
@@ -596,13 +1346,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>18639</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1677</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00402828868994498</v>
+        <v>0.0000000000110277413481629</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +1363,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>489</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00402828868994498</v>
+        <v>0.0000000000415548685104726</v>
       </c>
     </row>
     <row r="7">
@@ -630,13 +1380,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>490</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00402828868994498</v>
+        <v>0.000000000046385054534969</v>
       </c>
     </row>
     <row r="8">
@@ -647,13 +1397,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>156</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00402828868994498</v>
+        <v>0.0000000000500988297417418</v>
       </c>
     </row>
     <row r="9">
@@ -664,13 +1414,13 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0046982033607601</v>
+        <v>0.000000000980924096321818</v>
       </c>
     </row>
     <row r="10">
@@ -681,13 +1431,13 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>625</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00670543772725596</v>
+        <v>0.00000000318025789834503</v>
       </c>
     </row>
     <row r="11">
@@ -698,13 +1448,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>565</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00737368010456618</v>
+        <v>0.0000000135677381404466</v>
       </c>
     </row>
     <row r="12">
@@ -715,13 +1465,1526 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
+        <v>2249</v>
+      </c>
+      <c r="D12" t="n">
+        <v>265</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0000000222339277049301</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1545</v>
+      </c>
+      <c r="D13" t="n">
+        <v>194</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0000000240713873886644</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6314</v>
+      </c>
+      <c r="D14" t="n">
+        <v>643</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0000000424921932867518</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>26</v>
+      </c>
+      <c r="D15" t="n">
         <v>13</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.00870891268739382</v>
+      <c r="E15" t="n">
+        <v>0.0000000467405119216133</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0000000467405119216133</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6118</v>
+      </c>
+      <c r="D17" t="n">
+        <v>625</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0000000472009386146366</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2088</v>
+      </c>
+      <c r="D18" t="n">
+        <v>247</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.000000052241795405647</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>271</v>
+      </c>
+      <c r="D19" t="n">
+        <v>51</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0000000714581934412524</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2421</v>
+      </c>
+      <c r="D20" t="n">
+        <v>278</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.000000104917919232372</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>672</v>
+      </c>
+      <c r="D21" t="n">
+        <v>98</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.000000125726863818627</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>726</v>
+      </c>
+      <c r="D22" t="n">
+        <v>104</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.000000127522131500525</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>230</v>
+      </c>
+      <c r="D23" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.000000129062538013322</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>144</v>
+      </c>
+      <c r="D24" t="n">
+        <v>33</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.000000137443770629555</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5571</v>
+      </c>
+      <c r="D25" t="n">
+        <v>568</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.000000409021866155152</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>497</v>
+      </c>
+      <c r="D26" t="n">
+        <v>76</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.000000517500396962019</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>699</v>
+      </c>
+      <c r="D27" t="n">
+        <v>98</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.000000801168757505209</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.000000918832954944865</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2145</v>
+      </c>
+      <c r="D29" t="n">
+        <v>245</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0000010495657175606</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2126</v>
+      </c>
+      <c r="D30" t="n">
+        <v>243</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.00000110840785127021</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>115</v>
+      </c>
+      <c r="D31" t="n">
+        <v>27</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.00000111027628947785</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2277</v>
+      </c>
+      <c r="D32" t="n">
+        <v>257</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.00000142424585916848</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>33</v>
+      </c>
+      <c r="D33" t="n">
+        <v>13</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.00000145253191584028</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>24</v>
+      </c>
+      <c r="D34" t="n">
+        <v>11</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0000015646052224836</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>357</v>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.00000165339455155444</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>49</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.00000174585104666112</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>778</v>
+      </c>
+      <c r="D37" t="n">
+        <v>105</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.00000197822981013213</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="n">
+        <v>79</v>
+      </c>
+      <c r="D38" t="n">
+        <v>21</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.00000203855910494215</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" t="n">
+        <v>360</v>
+      </c>
+      <c r="D39" t="n">
+        <v>58</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.00000217115879252238</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="n">
+        <v>354</v>
+      </c>
+      <c r="D40" t="n">
+        <v>57</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.00000269807402733379</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>363</v>
+      </c>
+      <c r="D41" t="n">
+        <v>58</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.00000283752278068545</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>488</v>
+      </c>
+      <c r="D42" t="n">
+        <v>72</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.00000384735927939745</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2238</v>
+      </c>
+      <c r="D43" t="n">
+        <v>250</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.00000445943568483956</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.000004621453120137</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="n">
+        <v>861</v>
+      </c>
+      <c r="D45" t="n">
+        <v>112</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.00000521565882328259</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>592</v>
+      </c>
+      <c r="D46" t="n">
+        <v>83</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.00000554063223102309</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1189</v>
+      </c>
+      <c r="D47" t="n">
+        <v>145</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.00000791743222780248</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>882</v>
+      </c>
+      <c r="D48" t="n">
+        <v>113</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.00000952632694051</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2456</v>
+      </c>
+      <c r="D49" t="n">
+        <v>268</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0000117272100091077</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D50" t="n">
+        <v>220</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0000141006608145515</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="n">
+        <v>45</v>
+      </c>
+      <c r="D51" t="n">
+        <v>14</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.0000144948669553505</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="n">
+        <v>349</v>
+      </c>
+      <c r="D52" t="n">
+        <v>54</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0000158466039521356</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2247</v>
+      </c>
+      <c r="D53" t="n">
+        <v>247</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0000163897863467731</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="n">
+        <v>16</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.000019822852239734</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D55" t="n">
+        <v>211</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.0000224783292455464</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2217</v>
+      </c>
+      <c r="D56" t="n">
+        <v>243</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.0000236477075008866</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>59</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.0000250858179858459</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1866</v>
+      </c>
+      <c r="D58" t="n">
+        <v>209</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.0000253887185815995</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1613</v>
+      </c>
+      <c r="D59" t="n">
+        <v>184</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.0000288042698614072</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1123</v>
+      </c>
+      <c r="D60" t="n">
+        <v>135</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.0000328582988832189</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>115</v>
+      </c>
+      <c r="D61" t="n">
+        <v>24</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.000035479806376683</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>115</v>
+      </c>
+      <c r="D62" t="n">
+        <v>24</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.000035479806376683</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1276</v>
+      </c>
+      <c r="D63" t="n">
+        <v>150</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.0000377848192729873</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="n">
+        <v>664</v>
+      </c>
+      <c r="D64" t="n">
+        <v>87</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.0000447915666496078</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" t="n">
+        <v>140</v>
+      </c>
+      <c r="D65" t="n">
+        <v>27</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.000051890542825646</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1518</v>
+      </c>
+      <c r="D66" t="n">
+        <v>173</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.0000532387168645033</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="n">
+        <v>91</v>
+      </c>
+      <c r="D67" t="n">
+        <v>20</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.0000723479794536776</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" t="n">
+        <v>361</v>
+      </c>
+      <c r="D68" t="n">
+        <v>53</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.0000797307522128826</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="n">
+        <v>34</v>
+      </c>
+      <c r="D69" t="n">
+        <v>11</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.0000801653040812363</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4452</v>
+      </c>
+      <c r="D70" t="n">
+        <v>445</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.0000997260500931871</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1817</v>
+      </c>
+      <c r="D71" t="n">
+        <v>200</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.000105802403784916</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" t="n">
+        <v>47</v>
+      </c>
+      <c r="D72" t="n">
+        <v>13</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.000114091802413431</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" t="n">
+        <v>433</v>
+      </c>
+      <c r="D73" t="n">
+        <v>60</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.00014704933790789</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" t="n">
+        <v>26</v>
+      </c>
+      <c r="D74" t="n">
+        <v>9</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.00020008099958096</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1475</v>
+      </c>
+      <c r="D75" t="n">
+        <v>165</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.000202159114550967</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" t="n">
+        <v>8</v>
+      </c>
+      <c r="D76" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.000207398458429193</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" t="n">
+        <v>87</v>
+      </c>
+      <c r="D77" t="n">
+        <v>18</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.000361479466264115</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" t="n">
+        <v>59</v>
+      </c>
+      <c r="D78" t="n">
+        <v>14</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.000369242470445793</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4353</v>
+      </c>
+      <c r="D79" t="n">
+        <v>430</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.000382783852175704</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" t="n">
+        <v>13</v>
+      </c>
+      <c r="D80" t="n">
+        <v>6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.000399335418251196</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1124</v>
+      </c>
+      <c r="D81" t="n">
+        <v>128</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.000521677298865932</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.000630282037787038</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.000630282037787038</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+      <c r="D84" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.000805895723607496</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D85" t="n">
+        <v>8</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.000826150371846424</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" t="n">
+        <v>50</v>
+      </c>
+      <c r="D86" t="n">
+        <v>12</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.000854277502565611</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" t="n">
+        <v>117</v>
+      </c>
+      <c r="D87" t="n">
+        <v>21</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.000911678371050223</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" t="n">
+        <v>26</v>
+      </c>
+      <c r="D88" t="n">
+        <v>8</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.00110440342618663</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" t="n">
+        <v>273</v>
+      </c>
+      <c r="D89" t="n">
+        <v>39</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.00111664071625721</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" t="n">
+        <v>21</v>
+      </c>
+      <c r="D90" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.00133718823122958</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" t="n">
+        <v>11</v>
+      </c>
+      <c r="D91" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.00137329719228266</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" t="n">
+        <v>11</v>
+      </c>
+      <c r="D92" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.00137329719228266</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" t="n">
+        <v>137</v>
+      </c>
+      <c r="D93" t="n">
+        <v>23</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.00137479457414414</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" t="n">
+        <v>129</v>
+      </c>
+      <c r="D94" t="n">
+        <v>22</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.00140218919903081</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" t="n">
+        <v>7</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.00152825483691813</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" t="n">
+        <v>287</v>
+      </c>
+      <c r="D96" t="n">
+        <v>40</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.00155967146050608</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D97" t="n">
+        <v>142</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.00155997375317062</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" t="n">
+        <v>148</v>
+      </c>
+      <c r="D98" t="n">
+        <v>24</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.00178342157832253</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>103</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" t="n">
+        <v>84</v>
+      </c>
+      <c r="D99" t="n">
+        <v>16</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.00188961817319599</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" t="n">
+        <v>567</v>
+      </c>
+      <c r="D100" t="n">
+        <v>69</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.00196714512365643</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1554</v>
+      </c>
+      <c r="D101" t="n">
+        <v>165</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.00211060999965309</v>
       </c>
     </row>
   </sheetData>
@@ -754,427 +3017,1702 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4221</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000672430355427522</v>
+        <v>0.0000000000000000000000000000147566219344088</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>1153</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000775908475433154</v>
+        <v>0.000000000000000000000000000445069612852714</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C4" t="n">
-        <v>65</v>
+        <v>3125</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>436</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000852475499560973</v>
+        <v>0.000000000000000000000000000568657610215602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>831</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00134444082543206</v>
+        <v>0.00000000000000000000000000415723429700759</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>191</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00134444082543206</v>
+        <v>0.0000000000000000000000000051591594168543</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6422</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>755</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00134444082543206</v>
+        <v>0.00000000000000000000000000932965256659827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6054</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>716</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00134444082543206</v>
+        <v>0.000000000000000000000000119964273377508</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>2976</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>407</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00134444082543206</v>
+        <v>0.00000000000000000000000392766490151787</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>977</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00201603165204578</v>
+        <v>0.000000000000000000000013223157381378</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1666</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00201603165204578</v>
+        <v>0.0000000000000000000000440788026167513</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1720</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00201603165204578</v>
+        <v>0.000000000000000000000105913291139549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>6216</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>716</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00224515801963935</v>
+        <v>0.00000000000000000000032615706779713</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>2894</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>389</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00268720307717274</v>
+        <v>0.00000000000000000000148721825064772</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3185</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>419</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00268720307717274</v>
+        <v>0.00000000000000000000149750543246274</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>819</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>154</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00268720307717274</v>
+        <v>0.00000000000000000000361974747095159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>3045</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00335795534258954</v>
+        <v>0.00000000000000000000394791685288545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>639</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00335795534258954</v>
+        <v>0.0000000000000000000145578222043755</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>7631</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>837</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00335795534258954</v>
+        <v>0.0000000000000000000156230060020482</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>2578</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>352</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00402828868994498</v>
+        <v>0.0000000000000000000172643205562234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>4532</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>548</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00402828868994498</v>
+        <v>0.0000000000000000000232747162907524</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>3628</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>459</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0046982033607601</v>
+        <v>0.0000000000000000000238303210425006</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>4534</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>548</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0046982033607601</v>
+        <v>0.0000000000000000000257348442099766</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>597</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0046982033607601</v>
+        <v>0.0000000000000000000595400961180927</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C25" t="n">
-        <v>197</v>
+        <v>3635</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>458</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00752164463441505</v>
+        <v>0.000000000000000000060802867497479</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>6724</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>752</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00937590337429617</v>
+        <v>0.0000000000000000000610478512113286</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" t="n">
+        <v>6120</v>
+      </c>
+      <c r="D27" t="n">
+        <v>696</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0000000000000000000743927071205756</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" t="n">
+        <v>6749</v>
+      </c>
+      <c r="D28" t="n">
+        <v>753</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.000000000000000000111135575688995</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6708</v>
+      </c>
+      <c r="D29" t="n">
+        <v>748</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.000000000000000000198917609177358</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" t="n">
+        <v>533</v>
+      </c>
+      <c r="D30" t="n">
+        <v>112</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.000000000000000000230632384739652</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>136</v>
+      </c>
+      <c r="B31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D31" t="n">
+        <v>247</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.000000000000000000361626703083968</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7594</v>
+      </c>
+      <c r="D32" t="n">
+        <v>826</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.000000000000000000527270046305002</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2932</v>
+      </c>
+      <c r="D33" t="n">
+        <v>382</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.000000000000000000953232504973551</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1956</v>
+      </c>
+      <c r="D34" t="n">
+        <v>279</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.00000000000000000114649201858566</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2411</v>
+      </c>
+      <c r="D35" t="n">
+        <v>327</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.00000000000000000166280986332534</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" t="n">
+        <v>12399</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1234</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.00000000000000000177754664164473</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" t="n">
+        <v>653</v>
+      </c>
+      <c r="D37" t="n">
+        <v>126</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.00000000000000000204528891625164</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>143</v>
+      </c>
+      <c r="B38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" t="n">
+        <v>9311</v>
+      </c>
+      <c r="D38" t="n">
+        <v>971</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0000000000000000078526749501268</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1146</v>
+      </c>
+      <c r="D39" t="n">
+        <v>185</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.00000000000000000925250664666573</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D40" t="n">
+        <v>211</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.00000000000000000932152385823769</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2029</v>
+      </c>
+      <c r="D41" t="n">
+        <v>282</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0000000000000000259661288141264</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" t="n">
+        <v>12011</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1196</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0000000000000000287405268197494</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4852</v>
+      </c>
+      <c r="D43" t="n">
+        <v>564</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0000000000000000328894574299177</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D44" t="n">
+        <v>269</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0000000000000000416310973171907</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>150</v>
+      </c>
+      <c r="B45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" t="n">
+        <v>593</v>
+      </c>
+      <c r="D45" t="n">
+        <v>115</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0000000000000000455403370149674</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" t="n">
+        <v>432</v>
+      </c>
+      <c r="D46" t="n">
+        <v>93</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.0000000000000000556349224863505</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" t="n">
+        <v>433</v>
+      </c>
+      <c r="D47" t="n">
+        <v>93</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0000000000000000650622262971863</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" t="n">
+        <v>521</v>
+      </c>
+      <c r="D48" t="n">
+        <v>105</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0000000000000000702535411128026</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2093</v>
+      </c>
+      <c r="D49" t="n">
+        <v>285</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.000000000000000268516268608647</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>155</v>
+      </c>
+      <c r="B50" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1249</v>
+      </c>
+      <c r="D50" t="n">
+        <v>192</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.000000000000000378354418364114</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>156</v>
+      </c>
+      <c r="B51" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D51" t="n">
+        <v>220</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.00000000000000048125922850603</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>157</v>
+      </c>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1079</v>
+      </c>
+      <c r="D52" t="n">
+        <v>172</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.000000000000000501728977827352</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" t="n">
+        <v>513</v>
+      </c>
+      <c r="D53" t="n">
+        <v>102</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.000000000000000510532947610635</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" t="n">
+        <v>455</v>
+      </c>
+      <c r="D54" t="n">
+        <v>94</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.000000000000000604997098056772</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" t="n">
+        <v>12800</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1253</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.000000000000000743036747391964</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>161</v>
+      </c>
+      <c r="B56" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1144</v>
+      </c>
+      <c r="D56" t="n">
+        <v>179</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.000000000000000757351092174601</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1188</v>
+      </c>
+      <c r="D57" t="n">
+        <v>184</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.0000000000000007943578338935</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>163</v>
+      </c>
+      <c r="B58" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2523</v>
+      </c>
+      <c r="D58" t="n">
+        <v>327</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.00000000000000138217248853262</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>164</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1391</v>
+      </c>
+      <c r="D59" t="n">
+        <v>206</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.00000000000000158304497760218</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>165</v>
+      </c>
+      <c r="B60" t="s">
+        <v>107</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1551</v>
+      </c>
+      <c r="D60" t="n">
+        <v>223</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.00000000000000254913696424002</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>166</v>
+      </c>
+      <c r="B61" t="s">
+        <v>107</v>
+      </c>
+      <c r="C61" t="n">
+        <v>395</v>
+      </c>
+      <c r="D61" t="n">
+        <v>84</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.000000000000003895476473403</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>167</v>
+      </c>
+      <c r="B62" t="s">
+        <v>107</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2264</v>
+      </c>
+      <c r="D62" t="n">
+        <v>297</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.00000000000000824518342853863</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63" t="s">
+        <v>107</v>
+      </c>
+      <c r="C63" t="n">
+        <v>395</v>
+      </c>
+      <c r="D63" t="n">
+        <v>83</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.0000000000000116196164326115</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>169</v>
+      </c>
+      <c r="B64" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" t="n">
+        <v>600</v>
+      </c>
+      <c r="D64" t="n">
+        <v>110</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.0000000000000129320410537785</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B65" t="s">
+        <v>107</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5906</v>
+      </c>
+      <c r="D65" t="n">
+        <v>648</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.0000000000000188490340946412</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" t="s">
+        <v>107</v>
+      </c>
+      <c r="C66" t="n">
+        <v>927</v>
+      </c>
+      <c r="D66" t="n">
+        <v>149</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.0000000000000267900981463549</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>172</v>
+      </c>
+      <c r="B67" t="s">
+        <v>107</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4180</v>
+      </c>
+      <c r="D67" t="n">
+        <v>485</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.0000000000000272985413501005</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>173</v>
+      </c>
+      <c r="B68" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D68" t="n">
+        <v>161</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.0000000000000294006287931379</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" t="s">
+        <v>107</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D69" t="n">
+        <v>160</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.0000000000000310677555205842</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>175</v>
+      </c>
+      <c r="B70" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4122</v>
+      </c>
+      <c r="D70" t="n">
+        <v>479</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.000000000000033019039435377</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>176</v>
+      </c>
+      <c r="B71" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D71" t="n">
+        <v>159</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.0000000000000357426471790163</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>177</v>
+      </c>
+      <c r="B72" t="s">
+        <v>107</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1167</v>
+      </c>
+      <c r="D72" t="n">
+        <v>176</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.0000000000000437352489621757</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>178</v>
+      </c>
+      <c r="B73" t="s">
+        <v>107</v>
+      </c>
+      <c r="C73" t="n">
+        <v>646</v>
+      </c>
+      <c r="D73" t="n">
+        <v>114</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.000000000000064367219401329</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>179</v>
+      </c>
+      <c r="B74" t="s">
+        <v>107</v>
+      </c>
+      <c r="C74" t="n">
+        <v>630</v>
+      </c>
+      <c r="D74" t="n">
+        <v>112</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.0000000000000646033691334212</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>180</v>
+      </c>
+      <c r="B75" t="s">
+        <v>107</v>
+      </c>
+      <c r="C75" t="n">
+        <v>990</v>
+      </c>
+      <c r="D75" t="n">
+        <v>155</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.0000000000000741872103259918</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>181</v>
+      </c>
+      <c r="B76" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" t="n">
+        <v>372</v>
+      </c>
+      <c r="D76" t="n">
+        <v>78</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.0000000000000833716655382496</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" t="s">
+        <v>107</v>
+      </c>
+      <c r="C77" t="n">
+        <v>922</v>
+      </c>
+      <c r="D77" t="n">
+        <v>146</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.00000000000016743312639292</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>183</v>
+      </c>
+      <c r="B78" t="s">
+        <v>107</v>
+      </c>
+      <c r="C78" t="n">
+        <v>436</v>
+      </c>
+      <c r="D78" t="n">
+        <v>86</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.000000000000169257320948841</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>184</v>
+      </c>
+      <c r="B79" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" t="n">
+        <v>5700</v>
+      </c>
+      <c r="D79" t="n">
+        <v>623</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.000000000000207749107791581</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>185</v>
+      </c>
+      <c r="B80" t="s">
+        <v>107</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D80" t="n">
+        <v>208</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.000000000000271710837941526</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>186</v>
+      </c>
+      <c r="B81" t="s">
+        <v>107</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D81" t="n">
+        <v>259</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.000000000000308191245555696</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>187</v>
+      </c>
+      <c r="B82" t="s">
+        <v>107</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2174</v>
+      </c>
+      <c r="D82" t="n">
+        <v>281</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.000000000000313189825107281</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>188</v>
+      </c>
+      <c r="B83" t="s">
+        <v>107</v>
+      </c>
+      <c r="C83" t="n">
+        <v>303</v>
+      </c>
+      <c r="D83" t="n">
+        <v>67</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.000000000000357485195795222</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>189</v>
+      </c>
+      <c r="B84" t="s">
+        <v>107</v>
+      </c>
+      <c r="C84" t="n">
+        <v>340</v>
+      </c>
+      <c r="D84" t="n">
+        <v>72</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.000000000000455241173889296</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" t="s">
+        <v>107</v>
+      </c>
+      <c r="C85" t="n">
+        <v>499</v>
+      </c>
+      <c r="D85" t="n">
+        <v>93</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.000000000000567342615579558</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>191</v>
+      </c>
+      <c r="B86" t="s">
+        <v>107</v>
+      </c>
+      <c r="C86" t="n">
+        <v>300</v>
+      </c>
+      <c r="D86" t="n">
+        <v>66</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.000000000000687485907411693</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" t="s">
+        <v>107</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1786</v>
+      </c>
+      <c r="D87" t="n">
+        <v>239</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.000000000000716508951074729</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" t="s">
+        <v>107</v>
+      </c>
+      <c r="C88" t="n">
+        <v>344</v>
+      </c>
+      <c r="D88" t="n">
+        <v>72</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.000000000000831047470636848</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" t="s">
+        <v>107</v>
+      </c>
+      <c r="C89" t="n">
+        <v>805</v>
+      </c>
+      <c r="D89" t="n">
+        <v>130</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.00000000000093315068752255</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>195</v>
+      </c>
+      <c r="B90" t="s">
+        <v>107</v>
+      </c>
+      <c r="C90" t="n">
+        <v>2809</v>
+      </c>
+      <c r="D90" t="n">
+        <v>343</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.0000000000010435239430623</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>196</v>
+      </c>
+      <c r="B91" t="s">
+        <v>107</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1642</v>
+      </c>
+      <c r="D91" t="n">
+        <v>223</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.00000000000108800133352095</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>197</v>
+      </c>
+      <c r="B92" t="s">
+        <v>107</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1822</v>
+      </c>
+      <c r="D92" t="n">
+        <v>241</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.00000000000194764200298635</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>198</v>
+      </c>
+      <c r="B93" t="s">
+        <v>107</v>
+      </c>
+      <c r="C93" t="n">
+        <v>395</v>
+      </c>
+      <c r="D93" t="n">
+        <v>78</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.00000000000216675344320199</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>199</v>
+      </c>
+      <c r="B94" t="s">
+        <v>107</v>
+      </c>
+      <c r="C94" t="n">
+        <v>487</v>
+      </c>
+      <c r="D94" t="n">
+        <v>90</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.00000000000220695409249416</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>200</v>
+      </c>
+      <c r="B95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95" t="n">
+        <v>308</v>
+      </c>
+      <c r="D95" t="n">
+        <v>66</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.00000000000244824075540821</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>201</v>
+      </c>
+      <c r="B96" t="s">
+        <v>107</v>
+      </c>
+      <c r="C96" t="n">
+        <v>324</v>
+      </c>
+      <c r="D96" t="n">
+        <v>68</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.00000000000314587265039531</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>202</v>
+      </c>
+      <c r="B97" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" t="n">
+        <v>3685</v>
+      </c>
+      <c r="D97" t="n">
+        <v>426</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.00000000000375141508907482</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>203</v>
+      </c>
+      <c r="B98" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2749</v>
+      </c>
+      <c r="D98" t="n">
+        <v>334</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.00000000000432784831726079</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>204</v>
+      </c>
+      <c r="B99" t="s">
+        <v>107</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3374</v>
+      </c>
+      <c r="D99" t="n">
+        <v>394</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.00000000000838381358189405</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>205</v>
+      </c>
+      <c r="B100" t="s">
+        <v>107</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1821</v>
+      </c>
+      <c r="D100" t="n">
+        <v>238</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.00000000000942106105934445</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>206</v>
+      </c>
+      <c r="B101" t="s">
+        <v>107</v>
+      </c>
+      <c r="C101" t="n">
+        <v>340</v>
+      </c>
+      <c r="D101" t="n">
+        <v>69</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.0000000000111303265865063</v>
       </c>
     </row>
   </sheetData>
@@ -1207,240 +4745,1702 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12333</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1227</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000230139541575398</v>
+        <v>0.00000000000000000371531002435254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>6433</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>681</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000672430355427522</v>
+        <v>0.0000000000061221706400588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C4" t="n">
-        <v>73</v>
+        <v>5945</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>635</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00107376596929653</v>
+        <v>0.0000000000108496248732654</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C5" t="n">
-        <v>80</v>
+        <v>15643</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1452</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00128766816724015</v>
+        <v>0.000000000055516658699486</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C6" t="n">
-        <v>109</v>
+        <v>401</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00237193011133</v>
+        <v>0.000000000542726064627143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>742</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00268720307717274</v>
+        <v>0.00000000111547388396863</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>214</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>5530</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00603677763821342</v>
+        <v>0.0000000019326718174419</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>9718</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>953</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00603677763821342</v>
+        <v>0.0000000019477660736884</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>4825</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>514</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00670543772725596</v>
+        <v>0.00000000552870070496283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>217</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>2559</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>298</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00737368010456618</v>
+        <v>0.00000000800852479345751</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>218</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>2551</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>296</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00737368010456618</v>
+        <v>0.0000000130808906545195</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>219</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00737368010456618</v>
+        <v>0.0000000347435560873296</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>909</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00804150501102607</v>
+        <v>0.000000040560791636598</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="B15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4206</v>
+      </c>
+      <c r="D15" t="n">
+        <v>448</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.00000009002480726149</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2246</v>
+      </c>
+      <c r="D16" t="n">
+        <v>259</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.000000218515939884069</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" t="n">
+        <v>101</v>
+      </c>
+      <c r="D17" t="n">
+        <v>26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.000000257640582856109</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C18" t="n">
+        <v>434</v>
+      </c>
+      <c r="D18" t="n">
+        <v>68</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.00000084244658862672</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" t="n">
+        <v>291</v>
+      </c>
+      <c r="D19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.00000164877859873769</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" t="n">
+        <v>13987</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1287</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.00000189728621691327</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>227</v>
+      </c>
+      <c r="B21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" t="n">
+        <v>183</v>
+      </c>
+      <c r="D21" t="n">
+        <v>36</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.00000197458667892106</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" t="n">
+        <v>359</v>
+      </c>
+      <c r="D22" t="n">
+        <v>58</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.00000198374033753244</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C23" t="n">
+        <v>293</v>
+      </c>
+      <c r="D23" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0000020226842793296</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C24" t="n">
+        <v>694</v>
+      </c>
+      <c r="D24" t="n">
+        <v>95</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.00000333926775946741</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>231</v>
+      </c>
+      <c r="B25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3827</v>
+      </c>
+      <c r="D25" t="n">
+        <v>400</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.00000428865597009693</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>232</v>
+      </c>
+      <c r="B26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" t="n">
+        <v>12833</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1188</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.00000441563545251371</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>233</v>
+      </c>
+      <c r="B27" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" t="n">
+        <v>185</v>
+      </c>
+      <c r="D27" t="n">
+        <v>35</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.00000679209752679251</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2397</v>
+      </c>
+      <c r="D28" t="n">
+        <v>264</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.00000688188709090141</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1653</v>
+      </c>
+      <c r="D29" t="n">
+        <v>191</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.00000919870856176426</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>236</v>
+      </c>
+      <c r="B30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D30" t="n">
+        <v>133</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0000117638754553766</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>237</v>
+      </c>
+      <c r="B31" t="s">
+        <v>208</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D31" t="n">
+        <v>152</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.000015525037900639</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32" t="s">
+        <v>208</v>
+      </c>
+      <c r="C32" t="n">
+        <v>424</v>
+      </c>
+      <c r="D32" t="n">
+        <v>62</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.000023352080722055</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>239</v>
+      </c>
+      <c r="B33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" t="n">
+        <v>320</v>
+      </c>
+      <c r="D33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0000247193355687151</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>240</v>
+      </c>
+      <c r="B34" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" t="n">
+        <v>434</v>
+      </c>
+      <c r="D34" t="n">
+        <v>63</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0000252740148016436</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" t="n">
+        <v>14044</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1281</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.0000263057395362031</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>242</v>
+      </c>
+      <c r="B36" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1253</v>
+      </c>
+      <c r="D36" t="n">
+        <v>148</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0000335907825896304</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>243</v>
+      </c>
+      <c r="B37" t="s">
+        <v>208</v>
+      </c>
+      <c r="C37" t="n">
+        <v>14928</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0000628042189743981</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>244</v>
+      </c>
+      <c r="B38" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" t="n">
+        <v>579</v>
+      </c>
+      <c r="D38" t="n">
+        <v>77</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0000740961972257462</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>245</v>
+      </c>
+      <c r="B39" t="s">
+        <v>208</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4197</v>
+      </c>
+      <c r="D39" t="n">
+        <v>421</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.000121467526601738</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" t="n">
+        <v>11</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.000125013961197303</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>247</v>
+      </c>
+      <c r="B41" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" t="n">
+        <v>11</v>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.000125013961197303</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>248</v>
+      </c>
+      <c r="B42" t="s">
+        <v>208</v>
+      </c>
+      <c r="C42" t="n">
+        <v>11</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.000125013961197303</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>249</v>
+      </c>
+      <c r="B43" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.000125013961197303</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>250</v>
+      </c>
+      <c r="B44" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" t="n">
+        <v>774</v>
+      </c>
+      <c r="D44" t="n">
+        <v>96</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.00014883182782388</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>251</v>
+      </c>
+      <c r="B45" t="s">
+        <v>208</v>
+      </c>
+      <c r="C45" t="n">
+        <v>774</v>
+      </c>
+      <c r="D45" t="n">
+        <v>96</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.00014883182782388</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>252</v>
+      </c>
+      <c r="B46" t="s">
+        <v>208</v>
+      </c>
+      <c r="C46" t="n">
+        <v>530</v>
+      </c>
+      <c r="D46" t="n">
+        <v>70</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.000189887941646089</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>253</v>
+      </c>
+      <c r="B47" t="s">
+        <v>208</v>
+      </c>
+      <c r="C47" t="n">
+        <v>869</v>
+      </c>
+      <c r="D47" t="n">
+        <v>105</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.000202456077513918</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>254</v>
+      </c>
+      <c r="B48" t="s">
+        <v>208</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D48" t="n">
+        <v>151</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.000213566248786428</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>255</v>
+      </c>
+      <c r="B49" t="s">
+        <v>208</v>
+      </c>
+      <c r="C49" t="n">
+        <v>358</v>
+      </c>
+      <c r="D49" t="n">
+        <v>51</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.00022885593295637</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>256</v>
+      </c>
+      <c r="B50" t="s">
+        <v>208</v>
+      </c>
+      <c r="C50" t="n">
+        <v>914</v>
+      </c>
+      <c r="D50" t="n">
+        <v>109</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.000254402694789488</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" t="s">
+        <v>208</v>
+      </c>
+      <c r="C51" t="n">
+        <v>518</v>
+      </c>
+      <c r="D51" t="n">
+        <v>68</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.000277497205731781</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>258</v>
+      </c>
+      <c r="B52" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" t="n">
+        <v>495</v>
+      </c>
+      <c r="D52" t="n">
+        <v>65</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.000371112330947886</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>259</v>
+      </c>
+      <c r="B53" t="s">
+        <v>208</v>
+      </c>
+      <c r="C53" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.000433591622610173</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>260</v>
+      </c>
+      <c r="B54" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.000433591622610173</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>261</v>
+      </c>
+      <c r="B55" t="s">
+        <v>208</v>
+      </c>
+      <c r="C55" t="n">
+        <v>19545</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1708</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.000452061844923905</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>262</v>
+      </c>
+      <c r="B56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C56" t="n">
+        <v>41</v>
+      </c>
+      <c r="D56" t="n">
+        <v>11</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.000505677596366558</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>263</v>
+      </c>
+      <c r="B57" t="s">
+        <v>208</v>
+      </c>
+      <c r="C57" t="n">
+        <v>177</v>
+      </c>
+      <c r="D57" t="n">
+        <v>29</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.000534731100622722</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>264</v>
+      </c>
+      <c r="B58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" t="n">
+        <v>451</v>
+      </c>
+      <c r="D58" t="n">
+        <v>59</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.000741725094973212</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>265</v>
+      </c>
+      <c r="B59" t="s">
+        <v>208</v>
+      </c>
+      <c r="C59" t="n">
+        <v>451</v>
+      </c>
+      <c r="D59" t="n">
+        <v>59</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.000741725094973212</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>266</v>
+      </c>
+      <c r="B60" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60" t="n">
+        <v>31</v>
+      </c>
+      <c r="D60" t="n">
+        <v>9</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.000871695529589604</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>267</v>
+      </c>
+      <c r="B61" t="s">
+        <v>208</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D61" t="n">
+        <v>154</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.00115822841158047</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>268</v>
+      </c>
+      <c r="B62" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62" t="n">
+        <v>312</v>
+      </c>
+      <c r="D62" t="n">
+        <v>43</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.00133378652045803</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>269</v>
+      </c>
+      <c r="B63" t="s">
+        <v>208</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2445</v>
+      </c>
+      <c r="D63" t="n">
+        <v>250</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.00137578207155616</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>270</v>
+      </c>
+      <c r="B64" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" t="n">
+        <v>16</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.00148783539275697</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>271</v>
+      </c>
+      <c r="B65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.00152825483691813</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>272</v>
+      </c>
+      <c r="B66" t="s">
+        <v>208</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1660</v>
+      </c>
+      <c r="D66" t="n">
+        <v>176</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.00160943510232469</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>273</v>
+      </c>
+      <c r="B67" t="s">
+        <v>208</v>
+      </c>
+      <c r="C67" t="n">
+        <v>325</v>
+      </c>
+      <c r="D67" t="n">
         <v>44</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E67" t="n">
+        <v>0.00168792001502966</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>274</v>
+      </c>
+      <c r="B68" t="s">
+        <v>208</v>
+      </c>
+      <c r="C68" t="n">
+        <v>28</v>
+      </c>
+      <c r="D68" t="n">
+        <v>8</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.00188249954171318</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>275</v>
+      </c>
+      <c r="B69" t="s">
+        <v>208</v>
+      </c>
+      <c r="C69" t="n">
+        <v>254</v>
+      </c>
+      <c r="D69" t="n">
+        <v>36</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.00194457322389343</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>276</v>
+      </c>
+      <c r="B70" t="s">
+        <v>208</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1093</v>
+      </c>
+      <c r="D70" t="n">
+        <v>121</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.0020377635130528</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>277</v>
+      </c>
+      <c r="B71" t="s">
+        <v>208</v>
+      </c>
+      <c r="C71" t="n">
+        <v>55</v>
+      </c>
+      <c r="D71" t="n">
         <v>12</v>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.00804150501102607</v>
+      <c r="E71" t="n">
+        <v>0.00206993338955141</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>278</v>
+      </c>
+      <c r="B72" t="s">
+        <v>208</v>
+      </c>
+      <c r="C72" t="n">
+        <v>909</v>
+      </c>
+      <c r="D72" t="n">
+        <v>103</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.00208185272025952</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>279</v>
+      </c>
+      <c r="B73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2443</v>
+      </c>
+      <c r="D73" t="n">
+        <v>248</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.00211355156472556</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>280</v>
+      </c>
+      <c r="B74" t="s">
+        <v>208</v>
+      </c>
+      <c r="C74" t="n">
+        <v>109</v>
+      </c>
+      <c r="D74" t="n">
+        <v>19</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.00222068693736068</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>281</v>
+      </c>
+      <c r="B75" t="s">
+        <v>208</v>
+      </c>
+      <c r="C75" t="n">
+        <v>35</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.00223339995360758</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>282</v>
+      </c>
+      <c r="B76" t="s">
+        <v>208</v>
+      </c>
+      <c r="C76" t="n">
+        <v>388</v>
+      </c>
+      <c r="D76" t="n">
+        <v>50</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.00246723069862979</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>283</v>
+      </c>
+      <c r="B77" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2323</v>
+      </c>
+      <c r="D77" t="n">
+        <v>236</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.00261686361972031</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>284</v>
+      </c>
+      <c r="B78" t="s">
+        <v>208</v>
+      </c>
+      <c r="C78" t="n">
+        <v>79</v>
+      </c>
+      <c r="D78" t="n">
+        <v>15</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.00266686720105811</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>285</v>
+      </c>
+      <c r="B79" t="s">
+        <v>208</v>
+      </c>
+      <c r="C79" t="n">
+        <v>440</v>
+      </c>
+      <c r="D79" t="n">
+        <v>55</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.00303371397519325</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>286</v>
+      </c>
+      <c r="B80" t="s">
+        <v>208</v>
+      </c>
+      <c r="C80" t="n">
+        <v>13</v>
+      </c>
+      <c r="D80" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.00330691505965865</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>287</v>
+      </c>
+      <c r="B81" t="s">
+        <v>208</v>
+      </c>
+      <c r="C81" t="n">
+        <v>265</v>
+      </c>
+      <c r="D81" t="n">
+        <v>36</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.00398303608694057</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>288</v>
+      </c>
+      <c r="B82" t="s">
+        <v>208</v>
+      </c>
+      <c r="C82" t="n">
+        <v>25</v>
+      </c>
+      <c r="D82" t="n">
+        <v>7</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.00407869239826832</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>289</v>
+      </c>
+      <c r="B83" t="s">
+        <v>208</v>
+      </c>
+      <c r="C83" t="n">
+        <v>115</v>
+      </c>
+      <c r="D83" t="n">
+        <v>19</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.00412509749443867</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>290</v>
+      </c>
+      <c r="B84" t="s">
+        <v>208</v>
+      </c>
+      <c r="C84" t="n">
+        <v>14</v>
+      </c>
+      <c r="D84" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.00478397166607363</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>291</v>
+      </c>
+      <c r="B85" t="s">
+        <v>208</v>
+      </c>
+      <c r="C85" t="n">
+        <v>14</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.00478397166607363</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>292</v>
+      </c>
+      <c r="B86" t="s">
+        <v>208</v>
+      </c>
+      <c r="C86" t="n">
+        <v>46</v>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.00488802786862158</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>293</v>
+      </c>
+      <c r="B87" t="s">
+        <v>208</v>
+      </c>
+      <c r="C87" t="n">
+        <v>85</v>
+      </c>
+      <c r="D87" t="n">
+        <v>15</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.00548162770374354</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>294</v>
+      </c>
+      <c r="B88" t="s">
+        <v>208</v>
+      </c>
+      <c r="C88" t="n">
+        <v>85</v>
+      </c>
+      <c r="D88" t="n">
+        <v>15</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.00548162770374354</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>295</v>
+      </c>
+      <c r="B89" t="s">
+        <v>208</v>
+      </c>
+      <c r="C89" t="n">
+        <v>19880</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1726</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.00654658170884874</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>296</v>
+      </c>
+      <c r="B90" t="s">
+        <v>208</v>
+      </c>
+      <c r="C90" t="n">
+        <v>15</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.00667483981525478</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>297</v>
+      </c>
+      <c r="B91" t="s">
+        <v>208</v>
+      </c>
+      <c r="C91" t="n">
+        <v>112</v>
+      </c>
+      <c r="D91" t="n">
+        <v>18</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.00689909011846409</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>298</v>
+      </c>
+      <c r="B92" t="s">
+        <v>208</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.00735493916067857</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>299</v>
+      </c>
+      <c r="B93" t="s">
+        <v>208</v>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.00735493916067857</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>300</v>
+      </c>
+      <c r="B94" t="s">
+        <v>208</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.00735493916067857</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>301</v>
+      </c>
+      <c r="B95" t="s">
+        <v>208</v>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.00735493916067857</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>302</v>
+      </c>
+      <c r="B96" t="s">
+        <v>208</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.00735493916067857</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>303</v>
+      </c>
+      <c r="B97" t="s">
+        <v>208</v>
+      </c>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.00735493916067857</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>304</v>
+      </c>
+      <c r="B98" t="s">
+        <v>208</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.00735493916067857</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>305</v>
+      </c>
+      <c r="B99" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" t="n">
+        <v>165</v>
+      </c>
+      <c r="D99" t="n">
+        <v>24</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.00737137384450209</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>306</v>
+      </c>
+      <c r="B100" t="s">
+        <v>208</v>
+      </c>
+      <c r="C100" t="n">
+        <v>10</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.0074319476670026</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>307</v>
+      </c>
+      <c r="B101" t="s">
+        <v>208</v>
+      </c>
+      <c r="C101" t="n">
+        <v>28</v>
+      </c>
+      <c r="D101" t="n">
+        <v>7</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.00800868357536942</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +6456,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>308</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
